--- a/SDI_comparison_table_EPvsCTRL.xlsx
+++ b/SDI_comparison_table_EPvsCTRL.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,17 +499,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rostralanteriorcingulate_1</t>
+          <t>lateralorbitofrontal_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>-0.27</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -517,13 +515,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>parahippocampal_1</t>
+          <t>lateralorbitofrontal_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>-0.91</v>
+        <v>-1.17</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -533,13 +531,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>insula_1</t>
+          <t>parsorbitalis_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>-0.03</v>
+        <v>-0.54</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
@@ -549,16 +547,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Right-Amygdala</t>
+          <t>rostralanteriorcingulate_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>-2.34</v>
+        <v>-0.61</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.25</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="8">
@@ -567,17 +565,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Right-Hippocampus</t>
+          <t>caudalanteriorcingulate_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.66</v>
-      </c>
+        <v>-0.39</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -585,13 +581,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lateralorbitofrontal_1</t>
+          <t>fusiform_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>-0.64</v>
+        <v>-1.44</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
@@ -601,16 +597,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parstriangularis_1</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>parahippocampal_1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -619,15 +613,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parsopercularis_1</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.28</v>
-      </c>
+          <t>Right-Amygdala</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.28</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -635,20 +631,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>parahippocampal_1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.91</v>
-      </c>
+          <t>Right-Hippocampus</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>-0.88</v>
+        <v>-0.93</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.91</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="13">
@@ -657,16 +649,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Left-Amygdala</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>lateralorbitofrontal_1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>-0.64</v>
+      </c>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -675,16 +665,104 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Left-Hippocampus</t>
+          <t>lateralorbitofrontal_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.05</v>
+        <v>-0.44</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>parstriangularis_1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>parsopercularis_1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>parahippocampal_1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Left-Amygdala</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Left-Hippocampus</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
